--- a/WRExcel/RPC_GAME_EXCEL.xlsx
+++ b/WRExcel/RPC_GAME_EXCEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WRExcel\WRExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E344790B-9240-47EC-B8C3-E2797BBAEFF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B073D1-15BC-4675-8A74-B4990C3A1A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32550" yWindow="4670" windowWidth="28800" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32200" yWindow="4940" windowWidth="24850" windowHeight="15610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Struct" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="78">
   <si>
     <t>NULL</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -284,6 +284,58 @@
   </si>
   <si>
     <t>zone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>net_Count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>__int32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Loop1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_Info2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_Info1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_Vector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID[50]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vec[100]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Loop2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID[100]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_Info3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -609,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -628,7 +680,7 @@
     <col min="15" max="15" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -654,7 +706,123 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -680,7 +848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -712,7 +880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -732,7 +900,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -851,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF7DFA4-9A0B-4BDB-8272-4056E88C0B6F}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.4140625" customWidth="1"/>
@@ -969,25 +1137,25 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
@@ -995,90 +1163,106 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
         <v>54</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/WRExcel/RPC_GAME_EXCEL.xlsx
+++ b/WRExcel/RPC_GAME_EXCEL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WRExcel\WRExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B073D1-15BC-4675-8A74-B4990C3A1A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128A8F59-93FC-495D-B15A-D6277F6D5D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32200" yWindow="4940" windowWidth="24850" windowHeight="15610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36030" yWindow="3530" windowWidth="28800" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Struct" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="81">
   <si>
     <t>NULL</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -336,6 +336,18 @@
   </si>
   <si>
     <t>st_Info3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PROJECT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_Vector3F</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -734,7 +746,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -743,19 +755,25 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>72</v>
+      </c>
+      <c r="I3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
@@ -769,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
         <v>65</v>
@@ -778,10 +796,10 @@
         <v>67</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
@@ -795,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>65</v>
@@ -809,16 +827,42 @@
       <c r="H5" t="s">
         <v>74</v>
       </c>
-      <c r="I5" t="s">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
         <v>65</v>
       </c>
-      <c r="J5" t="s">
+      <c r="F6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" t="s">
         <v>75</v>
       </c>
-      <c r="K5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="K6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" t="s">
         <v>76</v>
       </c>
     </row>

--- a/WRExcel/RPC_GAME_EXCEL.xlsx
+++ b/WRExcel/RPC_GAME_EXCEL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WRExcel\WRExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128A8F59-93FC-495D-B15A-D6277F6D5D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B0BA71-BEBE-4F39-8961-0C286A8F4904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36030" yWindow="3530" windowWidth="28800" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35210" yWindow="4940" windowWidth="28800" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Struct" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="127">
   <si>
     <t>NULL</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -255,22 +255,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CHANGEPID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>st_CTS_ChangePid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>st_STC_ChangePid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NOT_FIND_PID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -287,55 +271,131 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHANGEZONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_STC_ChangeZone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_CTS_ChangeZone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 아이디 오류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLAYER_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZONE_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>존 아이디 오류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>__int32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_EntityInfo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Loop1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>net_Count</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>__int32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Loop1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>st_Info2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>st_Info1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>st_Vector</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID[50]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vec[100]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Loop2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID[100]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>st_Info3</t>
+    <t>info[50]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_ConnectInfo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CONNECTINFO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_STC_ConnectInfo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dir</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOVESTOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOVESTART</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_CTS_MoveStop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_STC_MoveStop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_CTS_MoveStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_STC_MoveStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_EQUAL_POSITION</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위치 가 다르다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PROJECT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_Vector3F</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -343,11 +403,135 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PROJECT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>st_Vector3F</t>
+    <t>speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBSERVER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CONNET_OBSERVER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_CTS_ObserverConnect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_STC_ObserverConnect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>length</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_Msg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>channel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHANGEINGZONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_STC_ChangeingZone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZONE_CHANEING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TELEPORT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_CTS_Teleport</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_STC_Teleport</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOI 안에 들어온 Player</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOI 밖으로 나간 Player</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOI_IN_PLAYER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOI_OUT_PLAYER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_STC_AoiInPlayer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_STC_AoiOutPlayer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_PlayerInfo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOI_IN_PLAYERS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOI 안에 들어온 Players 여러 개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_STC_AoiInPlayers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_STC_AoiOutPlayers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOI_OUT_PLAYERS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOI 밖으로 나간 Players 여러 개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OTHERMOVESTART</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다른 객체 움직임 시작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>st_STC_OtherMoveStart</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -673,28 +857,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
-    <col min="2" max="2" width="18.9140625" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.58203125" customWidth="1"/>
     <col min="4" max="4" width="27.58203125" customWidth="1"/>
     <col min="5" max="5" width="17.5" customWidth="1"/>
     <col min="6" max="6" width="17.58203125" customWidth="1"/>
     <col min="7" max="7" width="17.75" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="15.9140625" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="17.4140625" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" customWidth="1"/>
     <col min="12" max="12" width="11.33203125" customWidth="1"/>
     <col min="13" max="13" width="18.75" customWidth="1"/>
     <col min="15" max="15" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -718,9 +902,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
@@ -729,24 +913,30 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
         <v>43</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+      <c r="I2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -755,213 +945,617 @@
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" t="s">
         <v>43</v>
       </c>
-      <c r="F3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I6" t="s">
-        <v>65</v>
-      </c>
-      <c r="J6" t="s">
-        <v>75</v>
-      </c>
-      <c r="K6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="J7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
         <v>47</v>
       </c>
       <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
         <v>47</v>
       </c>
       <c r="F11" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s">
+        <v>117</v>
+      </c>
+      <c r="H20" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s">
+        <v>117</v>
+      </c>
+      <c r="H22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" t="s">
+        <v>82</v>
+      </c>
+      <c r="I23" t="s">
+        <v>92</v>
+      </c>
+      <c r="J23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J26" t="s">
+        <v>63</v>
+      </c>
+      <c r="K26" t="s">
+        <v>92</v>
+      </c>
+      <c r="L26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I30" t="s">
+        <v>92</v>
+      </c>
+      <c r="J30" t="s">
+        <v>64</v>
+      </c>
+      <c r="K30" t="s">
+        <v>92</v>
+      </c>
+      <c r="L30" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -972,34 +1566,194 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3095CB9C-57DF-42C7-A3A3-0F6AEE65EA25}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.9140625" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="33.08203125" customWidth="1"/>
-    <col min="4" max="4" width="19.58203125" customWidth="1"/>
+    <col min="4" max="4" width="42.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="B1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1">
+        <v>1000001</v>
+      </c>
+      <c r="D1">
+        <v>100001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1010,13 +1764,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE0DC10-87F9-4C62-BBAC-D66D3046F16E}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.25" customWidth="1"/>
     <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" customWidth="1"/>
+    <col min="4" max="4" width="28.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -1035,13 +1789,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
@@ -1049,9 +1803,62 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1066,8 +1873,8 @@
   <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.4140625" customWidth="1"/>
-    <col min="2" max="2" width="16.1640625" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
@@ -1181,10 +1988,10 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
@@ -1303,7 +2110,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
         <v>35</v>
